--- a/ProductionBuild/fullviewreits.result.xlsx
+++ b/ProductionBuild/fullviewreits.result.xlsx
@@ -1329,37 +1329,37 @@
         <v>5.849999904632568</v>
       </c>
       <c r="N8">
-        <v>0.350223705</v>
+        <v>0.35043084</v>
       </c>
       <c r="O8">
-        <v>0.428051195</v>
+        <v>0.42830436</v>
       </c>
       <c r="P8">
-        <v>0.46696494</v>
+        <v>0.46724112</v>
       </c>
       <c r="Q8">
-        <v>0.46696494</v>
+        <v>0.46724112</v>
       </c>
       <c r="R8">
-        <v>0.46696494</v>
+        <v>0.46724112</v>
       </c>
       <c r="S8">
-        <v>0.467045185</v>
+        <v>0.46732142</v>
       </c>
       <c r="T8">
-        <v>0.46705248</v>
+        <v>0.46732872</v>
       </c>
       <c r="U8">
-        <v>0.46705248</v>
+        <v>0.46732872</v>
       </c>
       <c r="V8">
-        <v>0.46705248</v>
+        <v>0.46732872</v>
       </c>
       <c r="W8">
-        <v>0.46705248</v>
+        <v>0.46732872</v>
       </c>
       <c r="X8">
-        <v>0.11676312</v>
+        <v>0.11683218</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Z8">
-        <v>0.4210170859090909</v>
+        <v>0.4212660945454546</v>
       </c>
       <c r="AA8">
-        <v>4.631187945</v>
+        <v>4.633927040000001</v>
       </c>
       <c r="AB8">
         <v>5.364799976348877</v>
@@ -1382,10 +1382,10 @@
         <v>0.4851999282836914</v>
       </c>
       <c r="AE8">
-        <v>5.116387873283691</v>
+        <v>5.119126968283692</v>
       </c>
       <c r="AF8">
-        <v>0.5116387873283691</v>
+        <v>0.5119126968283692</v>
       </c>
       <c r="AG8">
         <v>86</v>
@@ -1394,13 +1394,13 @@
         <v>503.0999917984009</v>
       </c>
       <c r="AI8">
-        <v>2.558193936641846</v>
+        <v>2.559563484141846</v>
       </c>
       <c r="AJ8">
-        <v>2.105085429545455</v>
+        <v>2.106330472727273</v>
       </c>
       <c r="AK8">
-        <v>4.6632793661873</v>
+        <v>4.665893956869118</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
